--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.102.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.102.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.102.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.102.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -602,11 +602,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE MASTERâ€™S OFFICE.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]95</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]95</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L35: isolated marker/symbol line :: 95</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]95</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -655,11 +659,7 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: practice in the Master's office :â€” July 1837</t>
-        </is>
-      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: %</t>
+          <t>L72: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -706,17 +706,13 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: in the Masterâ€™s office with indices in order to be referred ook.</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: -</t>
+          <t>L112: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -743,7 +739,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -753,15 +749,15 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜the Court.'</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L114: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -942,7 +938,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -981,7 +977,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1020,7 +1016,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
